--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Estudios-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,41; 18,74</t>
+          <t>10,17; 18,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>13,56; 22,64</t>
+          <t>14,04; 23,17</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17,31; 26,59</t>
+          <t>16,91; 26,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,67; 54,43</t>
+          <t>25,83; 53,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>41,21; 83,04</t>
+          <t>43,52; 84,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>43,7; 78,81</t>
+          <t>41,44; 77,24</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 9,68</t>
+          <t>5,06; 9,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -724,22 +724,22 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 13,65</t>
+          <t>2,57; 13,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45,21; 108,1</t>
+          <t>48,08; 112,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,92; 99,1</t>
+          <t>44,8; 99,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,9; 122,54</t>
+          <t>19,71; 124,87</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,27; 8,43</t>
+          <t>0,73; 8,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 5,24</t>
+          <t>-2,4; 5,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,65; 13,36</t>
+          <t>6,0; 13,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 193,35</t>
+          <t>9,31; 182,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,21; 76,7</t>
+          <t>-23,38; 77,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>39,65; 126,34</t>
+          <t>40,21; 126,64</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 14,09</t>
+          <t>10,12; 14,34</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 12,89</t>
+          <t>9,04; 13,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,55; 16,45</t>
+          <t>7,45; 16,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,24; 88,28</t>
+          <t>55,28; 88,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,64; 92,13</t>
+          <t>56,59; 91,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,09; 113,8</t>
+          <t>44,65; 114,45</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Estudios-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21,86</t>
+          <t>22,91</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>65,81%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,17; 18,68</t>
+          <t>9,96; 18,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>14,04; 23,17</t>
+          <t>14,06; 23,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,91; 26,36</t>
+          <t>18,18; 27,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,83; 53,68</t>
+          <t>25,39; 52,28</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,52; 84,65</t>
+          <t>42,79; 83,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>41,44; 77,24</t>
+          <t>48,08; 86,27</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,51</t>
+          <t>10,38</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>66,38%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 9,78</t>
+          <t>5,21; 9,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>5,3; 9,96</t>
+          <t>5,34; 9,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,57; 13,67</t>
+          <t>8,24; 12,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>48,08; 112,88</t>
+          <t>47,5; 112,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>44,8; 99,73</t>
+          <t>45,21; 97,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,71; 124,87</t>
+          <t>48,3; 88,96</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9,8</t>
+          <t>10,1</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,81%</t>
+          <t>79,79%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,73; 8,32</t>
+          <t>0,54; 8,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 5,62</t>
+          <t>-2,37; 5,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,0; 13,41</t>
+          <t>5,84; 13,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,31; 182,15</t>
+          <t>4,75; 179,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 77,01</t>
+          <t>-21,91; 74,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>40,21; 126,64</t>
+          <t>38,49; 124,96</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12,81</t>
+          <t>14,18</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,41%</t>
+          <t>77,97%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10,12; 14,34</t>
+          <t>10,01; 14,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,09</t>
+          <t>8,96; 12,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 16,38</t>
+          <t>12,29; 16,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55,28; 88,87</t>
+          <t>55,61; 89,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>56,59; 91,58</t>
+          <t>56,16; 90,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,65; 114,45</t>
+          <t>63,28; 93,4</t>
         </is>
       </c>
     </row>
